--- a/12627950.xlsx
+++ b/12627950.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e18bc73e7d535f/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCCA1151-9371-4C96-91A3-EFB9A8B956C6}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F11BA20-D899-4BF1-A234-22471C4BC6F3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2568,86 +2568,134 @@
       <c r="A46" s="8">
         <v>46285</v>
       </c>
-      <c r="B46" s="14"/>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
       <c r="C46" s="14">
         <v>120</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>55</v>
+      </c>
+      <c r="F46" s="14">
+        <v>250</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>50</v>
+      </c>
       <c r="I46" s="15">
-        <f t="shared" si="0"/>
-        <v>120</v>
+        <f t="shared" ref="I46:I47" si="4">IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
+        <v>1015</v>
       </c>
       <c r="J46" s="15">
-        <f t="shared" si="1"/>
-        <v>1320</v>
+        <f t="shared" ref="J46:J47" si="5">IF(I46="","",1440-I46)</f>
+        <v>425</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L46" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>46286</v>
       </c>
-      <c r="B47" s="14"/>
+      <c r="B47" s="14">
+        <v>400</v>
+      </c>
       <c r="C47" s="14">
         <v>120</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
+      <c r="D47" s="14">
+        <v>130</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>60</v>
+      </c>
       <c r="I47" s="15">
-        <f t="shared" si="0"/>
-        <v>120</v>
+        <f t="shared" si="4"/>
+        <v>1020</v>
       </c>
       <c r="J47" s="15">
-        <f t="shared" si="1"/>
-        <v>1320</v>
+        <f t="shared" si="5"/>
+        <v>420</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+      <c r="L47" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B48" s="14">
+        <v>450</v>
+      </c>
+      <c r="C48" s="14">
+        <v>120</v>
+      </c>
+      <c r="D48" s="14">
+        <v>120</v>
+      </c>
+      <c r="E48" s="14">
+        <v>50</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>80</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
+      <c r="A49" s="8">
+        <v>46288</v>
+      </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2669,7 +2717,9 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
+      <c r="A50" s="8">
+        <v>46289</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2691,7 +2741,9 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
+      <c r="A51" s="8">
+        <v>46290</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2713,7 +2765,9 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
+      <c r="A52" s="8">
+        <v>46291</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2735,7 +2789,9 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
+      <c r="A53" s="8">
+        <v>46292</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -3118,11 +3174,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3140,11 +3196,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3162,11 +3218,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3184,11 +3240,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3206,11 +3262,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3228,11 +3284,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3250,11 +3306,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3272,11 +3328,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3294,11 +3350,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3316,11 +3372,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3338,11 +3394,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3360,11 +3416,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3382,11 +3438,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3404,11 +3460,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3426,11 +3482,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3448,11 +3504,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3470,11 +3526,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3492,11 +3548,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3514,11 +3570,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3536,11 +3592,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3558,11 +3614,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3580,11 +3636,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3602,11 +3658,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3624,11 +3680,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3646,11 +3702,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3668,11 +3724,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3690,11 +3746,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3712,11 +3768,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3734,11 +3790,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3756,11 +3812,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3778,11 +3834,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3800,11 +3856,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3822,11 +3878,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3844,11 +3900,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3866,11 +3922,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3888,11 +3944,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3910,11 +3966,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3932,11 +3988,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3954,11 +4010,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3976,11 +4032,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3998,11 +4054,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4020,11 +4076,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4042,11 +4098,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4064,11 +4120,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4086,11 +4142,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4108,11 +4164,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4130,11 +4186,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4152,11 +4208,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4174,11 +4230,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4196,11 +4252,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4218,11 +4274,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4240,11 +4296,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4262,11 +4318,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4284,11 +4340,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4306,11 +4362,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4328,11 +4384,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4350,11 +4406,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4372,11 +4428,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4394,11 +4450,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4416,11 +4472,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4438,11 +4494,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4460,11 +4516,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4482,11 +4538,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4504,11 +4560,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4526,11 +4582,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4548,11 +4604,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4570,11 +4626,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4592,11 +4648,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4614,11 +4670,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4636,11 +4692,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4658,11 +4714,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4680,11 +4736,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4702,11 +4758,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4724,11 +4780,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4746,11 +4802,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4768,11 +4824,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4790,11 +4846,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4812,11 +4868,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4834,11 +4890,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4856,11 +4912,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4878,11 +4934,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4900,11 +4956,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4922,11 +4978,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4944,11 +5000,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4966,11 +5022,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4988,11 +5044,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5010,11 +5066,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5032,11 +5088,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5054,11 +5110,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5076,11 +5132,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5098,11 +5154,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5120,11 +5176,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5142,11 +5198,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5164,11 +5220,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5186,11 +5242,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5208,11 +5264,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5230,11 +5286,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5252,11 +5308,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5274,11 +5330,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5296,11 +5352,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5318,11 +5374,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5340,11 +5396,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5362,11 +5418,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5384,11 +5440,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5406,11 +5462,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5428,11 +5484,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5450,11 +5506,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5472,11 +5528,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5494,11 +5550,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5516,11 +5572,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5538,11 +5594,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5560,11 +5616,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5582,11 +5638,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5604,11 +5660,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5626,11 +5682,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5648,11 +5704,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5670,11 +5726,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5692,11 +5748,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5714,11 +5770,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5736,11 +5792,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5758,11 +5814,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5780,11 +5836,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5802,11 +5858,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5824,11 +5880,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5846,11 +5902,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5868,11 +5924,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5890,11 +5946,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5912,11 +5968,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5934,11 +5990,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5956,11 +6012,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5978,11 +6034,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6000,11 +6056,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6022,11 +6078,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6044,11 +6100,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6066,11 +6122,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6088,11 +6144,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6110,11 +6166,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6132,11 +6188,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6154,11 +6210,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6176,11 +6232,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6198,11 +6254,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6220,11 +6276,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6242,11 +6298,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6264,11 +6320,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6286,11 +6342,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6308,11 +6364,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6330,11 +6386,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6352,11 +6408,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6374,11 +6430,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6396,11 +6452,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6418,11 +6474,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6440,11 +6496,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6462,11 +6518,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6484,11 +6540,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6506,11 +6562,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6528,11 +6584,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6550,11 +6606,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6572,11 +6628,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6594,11 +6650,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6616,11 +6672,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6638,11 +6694,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6660,11 +6716,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6682,11 +6738,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6704,11 +6760,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6726,11 +6782,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6748,11 +6804,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6770,11 +6826,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6792,11 +6848,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6814,11 +6870,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6836,11 +6892,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6858,11 +6914,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6880,11 +6936,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6902,11 +6958,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6924,11 +6980,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6946,11 +7002,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6968,11 +7024,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6990,11 +7046,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7012,11 +7068,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7034,11 +7090,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7056,11 +7112,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7078,11 +7134,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7100,11 +7156,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7122,11 +7178,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7144,11 +7200,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7166,11 +7222,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7188,11 +7244,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7210,11 +7266,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7232,11 +7288,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7254,11 +7310,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7276,11 +7332,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7298,11 +7354,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7320,11 +7376,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7342,11 +7398,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7364,11 +7420,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7386,11 +7442,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7408,11 +7464,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7430,11 +7486,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7452,11 +7508,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7474,11 +7530,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7496,11 +7552,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7518,11 +7574,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7540,11 +7596,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7562,11 +7618,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7584,11 +7640,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7606,11 +7662,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7628,11 +7684,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7650,11 +7706,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7672,11 +7728,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7694,11 +7750,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7716,11 +7772,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7738,11 +7794,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7760,11 +7816,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7782,11 +7838,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7804,11 +7860,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7826,11 +7882,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7848,11 +7904,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7870,11 +7926,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7892,11 +7948,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7914,11 +7970,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7936,11 +7992,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7958,11 +8014,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7980,11 +8036,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8002,11 +8058,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8024,11 +8080,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8046,11 +8102,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8068,11 +8124,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8090,11 +8146,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8112,11 +8168,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8134,11 +8190,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8156,11 +8212,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8178,11 +8234,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8200,11 +8256,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8222,11 +8278,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8244,11 +8300,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8266,11 +8322,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8288,11 +8344,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8310,11 +8366,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8332,11 +8388,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8354,11 +8410,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8376,11 +8432,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8398,11 +8454,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8420,11 +8476,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8442,11 +8498,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8464,11 +8520,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8486,11 +8542,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8508,11 +8564,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8530,11 +8586,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8552,11 +8608,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8574,11 +8630,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8596,11 +8652,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8618,11 +8674,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8640,11 +8696,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8662,11 +8718,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8684,11 +8740,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8706,11 +8762,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8728,11 +8784,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8750,11 +8806,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8772,11 +8828,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8794,11 +8850,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8816,11 +8872,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8838,11 +8894,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8860,11 +8916,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8882,11 +8938,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8904,11 +8960,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8926,11 +8982,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8948,11 +9004,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8970,11 +9026,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8992,11 +9048,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9014,11 +9070,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9036,11 +9092,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9058,11 +9114,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9080,11 +9136,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9102,11 +9158,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9124,11 +9180,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9146,11 +9202,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9168,11 +9224,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9190,11 +9246,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9212,11 +9268,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9234,11 +9290,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9256,11 +9312,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9278,11 +9334,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9300,11 +9356,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9322,11 +9378,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9344,11 +9400,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9366,11 +9422,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9388,11 +9444,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9410,11 +9466,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9432,11 +9488,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9454,11 +9510,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9476,11 +9532,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9498,11 +9554,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9520,11 +9576,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9542,11 +9598,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9564,11 +9620,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9586,11 +9642,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9608,11 +9664,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9630,11 +9686,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9652,11 +9708,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9674,11 +9730,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9696,11 +9752,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9718,11 +9774,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9740,11 +9796,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9762,11 +9818,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9784,11 +9840,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9806,11 +9862,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9828,11 +9884,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9850,11 +9906,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9872,11 +9928,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9894,11 +9950,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9916,11 +9972,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9938,11 +9994,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9960,11 +10016,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9982,11 +10038,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10004,11 +10060,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10026,11 +10082,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10048,11 +10104,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10070,11 +10126,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10092,11 +10148,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10114,11 +10170,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10136,11 +10192,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10158,11 +10214,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10180,11 +10236,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10202,11 +10258,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10224,11 +10280,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10246,11 +10302,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10268,11 +10324,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10290,11 +10346,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10312,11 +10368,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10334,11 +10390,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10356,11 +10412,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10378,11 +10434,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10400,11 +10456,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12627950.xlsx
+++ b/12627950.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e18bc73e7d535f/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F11BA20-D899-4BF1-A234-22471C4BC6F3}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59D8DAF7-820D-4D2F-A67E-B5AD94186E75}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>NISHANT THAKUR</t>
+  </si>
+  <si>
+    <t>SATISFIED</t>
   </si>
 </sst>
 </file>
@@ -2696,24 +2699,44 @@
       <c r="A49" s="8">
         <v>46288</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>120</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>45</v>
+      </c>
+      <c r="F49" s="14">
+        <v>250</v>
+      </c>
+      <c r="G49" s="14">
+        <v>5</v>
+      </c>
+      <c r="H49" s="14">
+        <v>120</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>365</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">

--- a/12627950.xlsx
+++ b/12627950.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e18bc73e7d535f/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59D8DAF7-820D-4D2F-A67E-B5AD94186E75}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38B296CC-8440-485F-BB05-A06AA618A5F1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2743,20 +2743,34 @@
       <c r="A50" s="8">
         <v>46289</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="B50" s="14">
+        <v>450</v>
+      </c>
+      <c r="C50" s="14">
+        <v>120</v>
+      </c>
+      <c r="D50" s="14">
+        <v>160</v>
+      </c>
+      <c r="E50" s="14">
+        <v>45</v>
+      </c>
+      <c r="F50" s="14">
+        <v>150</v>
+      </c>
+      <c r="G50" s="14">
+        <v>3</v>
+      </c>
+      <c r="H50" s="14">
+        <v>55</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>460</v>
       </c>
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>

--- a/12627950.xlsx
+++ b/12627950.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e18bc73e7d535f/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38B296CC-8440-485F-BB05-A06AA618A5F1}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B7DCC1-6B7F-44FB-8F56-299BC189DC40}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -203,6 +203,15 @@
   </si>
   <si>
     <t>SATISFIED</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -2772,33 +2781,59 @@
         <f t="shared" si="1"/>
         <v>460</v>
       </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+      <c r="K50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>46290</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="B51" s="14">
+        <v>420</v>
+      </c>
+      <c r="C51" s="14">
+        <v>120</v>
+      </c>
+      <c r="D51" s="14">
+        <v>150</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>200</v>
+      </c>
+      <c r="G51" s="14">
+        <v>4</v>
+      </c>
+      <c r="H51" s="14">
+        <v>55</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>465</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
